--- a/data/trans_orig/IP1021_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1021_2023-Habitat-trans_orig.xlsx
@@ -735,7 +735,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4950</t>
+          <t>4961</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>451</t>
+          <t>452</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5055</t>
+          <t>5596</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -820,7 +820,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,18%</t>
         </is>
       </c>
     </row>
@@ -843,7 +843,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>112330</t>
+          <t>112319</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>252102</t>
+          <t>251561</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>256706</t>
+          <t>256705</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1397</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7613</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>8131</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3830</t>
+          <t>4108</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13513</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>182899</t>
+          <t>182519</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>189015</t>
+          <t>189115</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>246892</t>
+          <t>246904</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>253799</t>
+          <t>253960</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>432035</t>
+          <t>432147</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>441718</t>
+          <t>441440</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>2581</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11830</t>
+          <t>11738</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>807</t>
+          <t>827</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8933</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4666</t>
+          <t>4916</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16855</t>
+          <t>17332</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,62%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>177755</t>
+          <t>177847</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>186886</t>
+          <t>187004</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>176353</t>
+          <t>176180</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>184479</t>
+          <t>184459</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,18%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>358016</t>
+          <t>357539</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>370205</t>
+          <t>369955</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>516</t>
+          <t>525</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4470</t>
+          <t>5158</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2249</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11154</t>
+          <t>12274</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14219</t>
+          <t>13691</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,92%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>163492</t>
+          <t>162804</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>167446</t>
+          <t>167437</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>170084</t>
+          <t>168964</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>178989</t>
+          <t>178644</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>334982</t>
+          <t>335510</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>345174</t>
+          <t>345610</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8460</t>
+          <t>8534</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20236</t>
+          <t>19397</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7345</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21086</t>
+          <t>20776</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18255</t>
+          <t>17531</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35664</t>
+          <t>35836</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>645104</t>
+          <t>645943</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>656880</t>
+          <t>656806</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>740350</t>
+          <t>740660</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>754323</t>
+          <t>754091</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1391112</t>
+          <t>1390940</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1408521</t>
+          <t>1409245</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1021_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP1021_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>446</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4961</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1869</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>478</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4980</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,54%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>1869</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>452</t>
+          <t>482</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>5274</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>125350</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>115479</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>112319</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>116834</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>119202</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>116091</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>120593</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,46%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,77%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>139877</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>99,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>255356</t>
+          <t>244552</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>251561</t>
+          <t>241147</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>256705</t>
+          <t>245939</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125350</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125350</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125350</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>170</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>139877</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>139877</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>139877</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257157</t>
+          <t>246421</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257157</t>
+          <t>246421</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257157</t>
+          <t>246421</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3298</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1082</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>7797</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,29%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3730</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1397</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7993</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,96%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3504</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1075</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8131</t>
+          <t>7678</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>7234</t>
+          <t>6936</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4108</t>
+          <t>3757</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>12659</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,0%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>233908</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>229409</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>236124</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,71%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>273</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>186782</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>182519</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>189115</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,04%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,8%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>338</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>251531</t>
+          <t>180775</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>246904</t>
+          <t>176735</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>253960</t>
+          <t>182964</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>438314</t>
+          <t>414683</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>432147</t>
+          <t>408960</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>441440</t>
+          <t>417862</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2467</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>553</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8108</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,82%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5834</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2581</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11738</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>11518</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
+          <t>3,85%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
           <t>1,78%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>9131</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>4550</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17332</t>
+          <t>14958</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -1519,74 +1519,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>165874</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>160233</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>167788</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,18%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,67%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>217</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>183751</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>177847</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>187004</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>96,92%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>93,81%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,64%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>222</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>181989</t>
+          <t>150190</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>176180</t>
+          <t>144686</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>184459</t>
+          <t>153424</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
+          <t>96,15%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>92,63%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
           <t>98,22%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>95,09%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>99,55%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>439</t>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>365740</t>
+          <t>316065</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>357539</t>
+          <t>309587</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>369955</t>
+          <t>319995</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>226</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>189585</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>156204</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>374871</t>
+          <t>324545</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>5499</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2397</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>11185</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>6,6%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>1720</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>5158</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,31%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>5942</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2594</t>
+          <t>480</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12274</t>
+          <t>4995</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>7662</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3591</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13691</t>
+          <t>13979</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>163877</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>158191</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>166979</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,75%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>93,4%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,58%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>237</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>166242</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>162804</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>167437</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>98,98%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,93%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,69%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>175296</t>
+          <t>165429</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>168964</t>
+          <t>162150</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>178644</t>
+          <t>166665</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>341539</t>
+          <t>329306</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>335510</t>
+          <t>322542</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>345610</t>
+          <t>332881</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11263</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6666</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>19304</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,61%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>13084</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8534</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>19397</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,97%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12743</t>
+          <t>13236</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7345</t>
+          <t>8451</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20776</t>
+          <t>20185</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>25827</t>
+          <t>24500</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17531</t>
+          <t>17123</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35836</t>
+          <t>33763</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>689010</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>680969</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>693607</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,39%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,24%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>920</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>652256</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>645943</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>656806</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>98,03%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,08%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,72%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>961</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>748693</t>
+          <t>615597</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>740660</t>
+          <t>608648</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>754091</t>
+          <t>620382</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1400949</t>
+          <t>1304606</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1390940</t>
+          <t>1295343</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1409245</t>
+          <t>1311983</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700273</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700273</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700273</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665340</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761436</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761436</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761436</t>
+          <t>628833</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1426776</t>
+          <t>1329106</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1426776</t>
+          <t>1329106</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1426776</t>
+          <t>1329106</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
